--- a/data/trans_camb/P1409-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1409-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,69</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,12</t>
+          <t>-0,37; 3,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,39</t>
+          <t>0,81; 5,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,91</t>
+          <t>-0,6; 3,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,29</t>
+          <t>-0,73; 2,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,51</t>
+          <t>-0,13; 2,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,22</t>
+          <t>0,45; 3,0</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>155,43%</t>
+          <t>142,3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>79,44%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 266,44</t>
+          <t>-16,41; 290,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,79; 394,38</t>
+          <t>22,92; 446,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 177,89</t>
+          <t>-21,35; 184,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 157,84</t>
+          <t>-24,43; 131,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 159,23</t>
+          <t>-4,98; 147,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 202,68</t>
+          <t>15,52; 184,71</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,99</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,86</t>
+          <t>-0,72; 1,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,35</t>
+          <t>1,12; 5,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,54</t>
+          <t>-0,09; 3,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,5</t>
+          <t>-0,48; 2,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,08</t>
+          <t>0,06; 2,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,91</t>
+          <t>0,85; 3,25</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>118,85%</t>
+          <t>169,42%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 153,72</t>
+          <t>-34,83; 153,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 324,29</t>
+          <t>39,3; 411,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 169,68</t>
+          <t>-5,42; 166,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 126,32</t>
+          <t>-14,69; 119,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 109,63</t>
+          <t>0,9; 125,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 157,45</t>
+          <t>28,82; 173,71</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>2,29</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,33</t>
+          <t>-1,02; 1,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,69</t>
+          <t>0,16; 3,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,4</t>
+          <t>-0,35; 3,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,44</t>
+          <t>1,22; 4,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,92</t>
+          <t>-0,36; 1,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,14</t>
+          <t>1,08; 3,57</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>151,4%</t>
+          <t>122,36%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>120,02%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>120,4%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 197,79</t>
+          <t>-53,53; 172,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,3; 550,67</t>
+          <t>-1,64; 439,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 191,87</t>
+          <t>-11,05; 199,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 180,76</t>
+          <t>34,07; 303,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 132,19</t>
+          <t>-16,44; 129,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,18; 215,14</t>
+          <t>39,63; 265,31</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>2,02</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,27</t>
+          <t>-1,07; 2,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,18</t>
+          <t>-0,88; 2,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,49</t>
+          <t>-0,58; 2,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 27,13</t>
+          <t>1,48; 4,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,94</t>
+          <t>-0,36; 1,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 16,73</t>
+          <t>0,85; 3,26</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>306,72%</t>
+          <t>107,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>184,81%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 125,04</t>
+          <t>-30,66; 114,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 120,04</t>
+          <t>-27,83; 121,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 106,25</t>
+          <t>-16,3; 125,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82,18; 1097,91</t>
+          <t>36,75; 201,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 83,16</t>
+          <t>-12,34; 83,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,29; 605,32</t>
+          <t>24,85; 145,45</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,01</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,35</t>
+          <t>-0,11; 1,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,84</t>
+          <t>1,09; 2,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,15</t>
+          <t>0,46; 2,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 10,75</t>
+          <t>1,21; 2,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,54</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,59</t>
+          <t>1,38; 2,6</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>101,71%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131,84%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>116,63%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 83,14</t>
+          <t>-4,99; 83,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31,05; 170,16</t>
+          <t>48,32; 179,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,84; 90,63</t>
+          <t>14,74; 94,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47,02; 397,25</t>
+          <t>36,71; 127,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,43; 74,24</t>
+          <t>14,04; 73,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,6; 302,03</t>
+          <t>53,7; 126,17</t>
         </is>
       </c>
     </row>
